--- a/config/universe-generated/templates/UniverseEvidence.xlsx
+++ b/config/universe-generated/templates/UniverseEvidence.xlsx
@@ -38,16 +38,16 @@
     <t>id</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>e3f80e1176525292</t>
+    <t>a150dc1613038bec</t>
   </si>
   <si>
     <t>#name</t>
@@ -101,7 +101,7 @@
     <t>enum&lt;UniverseDataQuality&gt;</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
@@ -134,7 +134,7 @@
     <t>UniverseContentAudit</t>
   </si>
   <si>
-    <t>aaaebf829c6c5b64</t>
+    <t>c721728e2201c8b4</t>
   </si>
   <si>
     <t>content_stable_key</t>
@@ -191,7 +191,7 @@
     <t>UniverseCoverage</t>
   </si>
   <si>
-    <t>48259865a9f33b6c</t>
+    <t>9f39f4212a648086</t>
   </si>
   <si>
     <t>category</t>
@@ -218,7 +218,7 @@
     <t>UniverseReviewFixture</t>
   </si>
   <si>
-    <t>008bd7df6bd5ef86</t>
+    <t>2b007db800334c8a</t>
   </si>
   <si>
     <t>mechanic_family</t>
@@ -248,7 +248,7 @@
     <t>UniversePackFile</t>
   </si>
   <si>
-    <t>fa5ae685e543ab2b</t>
+    <t>d4994c4eaf8dbc6b</t>
   </si>
   <si>
     <t>relative_path</t>
